--- a/excel/salesforce_import_sample.xlsx
+++ b/excel/salesforce_import_sample.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1949,6 +1949,751 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>A제조 본사·사무동 복합기 MPS 구축</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>ACC-0001</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>PRT</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>직판</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>B2B기업</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>복합기·MPS</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>WF-C879R</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>740000000</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>매출 인식</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>부서별 개별 프린터 난립, 출력비용 관리 불가</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>보안출력·관제 SW 포함 5년 계약</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>기존고객</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>1분기 납품·검수 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>F대학병원 병동 복합기 MPS 5년 계약</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>ACC-0008</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>PRT</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>총판</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Q오피스솔루션</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>B2B기업</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>복합기·MPS</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>AM-C400</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>920000000</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>매출 인식</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>병동별 노후 장비 혼재, 유지비 급증</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>의료정보 보안출력 필수, 24시간 A/S</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>기존고객</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>2월 계약·상반기 매출 인식 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>경기OO교육청 중학교 전자교탁 프로젝터 240대</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>ACC-0003</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>PJT</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>직판</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>B2G공공</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>교육용 프로젝터</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>EB-770F</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>680000000</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>매출 인식</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>중학교 전자교탁 사업 1차분 발주</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>초단초점, 전자펜 인터랙티브</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>기존고객</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>4월 낙찰·납품 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>OO시청 시민홀 대형 레이저 프로젝터</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>ACC-0004</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>PJT</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>총판</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Q오피스솔루션</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>B2G공공</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>비즈니스 프로젝터</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>EB-PU2220B</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>660000000</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>계약 완료(수주)</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>시민홀 리모델링에 따른 대형 영상장비 신설</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>20,000루멘, WUXGA, 스택 투사</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>기존고객</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>5월 수주, 3분기 설치 예정</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>C전자부품 SCARA 1차 라인 증설 확정분</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>ACC-0005</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>RBT</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>직판</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>B2B기업</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>SCARA 로봇</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>GX4-B351S</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>590000000</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>계약 완료(수주)</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1차 도입 라인 성과 확인 후 확정 발주</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>기존 6대와 동일 사양·통합 제어</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>기존고객</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>6월 수주, 4분기 설치</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>D디스플레이 헤드모듈 상반기 정기 공급</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>ACC-0006</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>CMP</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>직판</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>B2B기업</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>잉크젯 헤드(부품)</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>PrecisionCore 헤드모듈</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>560000000</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>매출 인식</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>기존 라인 소모성 헤드모듈 정기 교체 수요</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>기존 QUAL 통과 사양 동일</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>기존고객</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>연간 공급계약 상반기분 인식</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>E물류 1·2센터 라벨프린터 교체</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>ACC-0007</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>PRT</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>총판</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>P총판상사</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>B2B기업</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>컬러 라벨프린터</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>CW-C6500</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>계약 완료(수주)</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>기존 장비 노후로 인쇄 품질 저하</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>WMS 연동 유지</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>기존고객</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>6월 수주, 순차 교체 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>C전자부품 협력사 GX4 로봇 2대</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>ACC-0005</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>RBT</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>총판</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>P총판상사</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>B2B기업</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>SCARA 로봇</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>GX4-B351S</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>90000000</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>매출 인식</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>협력사 소형 조립 셀 자동화</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>표준 사양</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>기존고객</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>협력사 소개 건, 납품 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>A제조 후공정 잉크젯 1차 도입분</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>ACC-0001</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>PRT</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>직판</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>B2B기업</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>산업용 잉크젯</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>WF-C21000</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>520000000</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>계약 완료(수주)</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>증설 라인 가동 전 선행 도입 물량</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>본계약과 동일 사양</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>기존고객</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>증설 본건(OPP-2026-0001)의 선행 발주분</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
